--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_157_Taiwan.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_157_Taiwan.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb0142f42b4594088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbae1b7cc070b4c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rca61639275e84e61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcd0803d881f4437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R08d0e6c51b1946ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R712725d0fefb4737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rddc996a6b2aa4820"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc94c7a8f54164dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf6b3e9b3b68a40e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4236384ceb684c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ree731456d5ed4cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2e0a55696721450e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ157CommercialTable" displayName="EEZ157CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ157CommercialTable" displayName="EEZ157CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ157FunctionalTable" displayName="EEZ157FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ157FunctionalTable" displayName="EEZ157FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ157ValidationTable" displayName="EEZ157ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ157ValidationTable" displayName="EEZ157ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10677,7 +10631,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74df383998da4459"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47f326adac484236"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10687,20 +10641,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10708,552 +10652,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>87817.24889998531</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1400158068965975</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.04345069829526</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>87817.24889998531</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.04414417612517</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$150,A2,'Species'!$U$2:$U$150))</x:f>
-        <x:v>12122656.968300242</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1400158068965975</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.04345069829526</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12122596.068985045</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>60.89931519702077</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000050236199285</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000005023619928476221</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>93507.70411843601</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.067222012226361</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>116.74062450065767</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>93507.70411843601</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>222.5816826047746</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$150,A3,'Species'!$U$2:$U$150))</x:f>
-        <x:v>20813102.1191909</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.067222012226361</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>116.74062450065767</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>10916147.77440894</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>9896954.344781961</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.906634331937471</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.9066343319374711</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>438.59408739</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6403766657148733</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>436.89458876792884</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>438.59408739</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>550.3240317398725</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$150,A4,'Species'!$U$2:$U$150))</x:f>
-        <x:v>241368.86646973476</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6403766657148733</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>436.89458876792884</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>191619.3834462991</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>49749.48302343566</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2596265687149435</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.25962656871494344</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>10841.8946353881</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.395743652666805</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>248.73886749933132</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>10841.8946353881</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>388.37177951793325</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$150,A5,'Species'!$U$2:$U$150))</x:f>
-        <x:v>4210685.9128916105</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.395743652666805</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>248.73886749933132</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2696800.5931535116</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1513885.319738099</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.5613634629054396</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.5613634629054396</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5949.4582267377</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.3969608250956194</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>24.94369715789217</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5949.4582267377</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>38.10585759385926</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$150,A6,'Species'!$U$2:$U$150))</x:f>
-        <x:v>226709.20794868123</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.3969608250956194</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>24.94369715789217</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>148401.48426127536</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>78307.72368740587</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.527674801079061</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.527674801079061</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>265931.11996955157</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5357122146732554</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>343.33036456823635</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>265931.11996955157</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>506.5498538127133</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$150,A7,'Species'!$U$2:$U$150))</x:f>
-        <x:v>134707369.94482747</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5357122146732554</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>343.33036456823635</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>91302228.36918554</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>43405141.57564193</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.4754006813517286</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.47540068135172864</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>483101.31797672884</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6977033521100138</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>498.54383726899147</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>483101.31797672884</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>918.8390880486724</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$150,A8,'Species'!$U$2:$U$150))</x:f>
-        <x:v>443892374.4448492</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6977033521100138</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>498.54383726899147</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>240847184.8538256</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>203045189.5910236</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8430457250901866</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8430457250901865</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>20514.115936836595</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.050764617126698</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1123.99561548236</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>20514.115936836595</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1125.7495501222356</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$150,A9,'Species'!$U$2:$U$150))</x:f>
-        <x:v>23093756.78704918</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.050764617126698</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1123.99561548236</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>23057776.36850114</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>35980.41854804009</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0015604461580776</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0015604461580776003</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6741.1298863431</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.259665762940855</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1818.3009387254872</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6741.1298863431</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1848.6802673161549</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$150,A10,'Species'!$U$2:$U$150))</x:f>
-        <x:v>12462193.800297683</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.259665762940855</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1818.3009387254872</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>12257402.800408095</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>204790.99988958798</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0167075361089357</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.016707536108935713</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26fbcdb5591a46b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e6814b1b7424c80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11263,20 +10848,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11284,1038 +10859,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>25260.042447150496</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.829053534647218</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>674.6111805981801</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>25260.042447150496</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>767.5190162615611</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$150,A2,'Species'!$U$2:$U$150))</x:f>
-        <x:v>19387562.929762226</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.829053534647218</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>674.6111805981801</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>17040707.05723234</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2346855.8725298867</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1377205690261452</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.13772056902614524</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>94611.6437785637</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.249281985775047</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1775.3418295201434</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>94611.6437785637</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2271.9542916040186</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$150,A3,'Species'!$U$2:$U$150))</x:f>
-        <x:v>214953330.11841846</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.249281985775047</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1775.3418295201434</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>167968008.75974336</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>46985321.35867509</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2797277987969813</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.27972779879698134</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>19527.3156940252</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.3704539517755485</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2346.6804310739653</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>19527.3156940252</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2373.8629828800463</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$150,A4,'Species'!$U$2:$U$150))</x:f>
-        <x:v>46355171.881059006</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.3704539517755485</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2346.6804310739653</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>45824369.610572465</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>530802.2704865411</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.011583405838366</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.01158340583836588</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>50390.304235726915</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.3526366633657885</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2252.354073831527</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>50390.304235726915</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2269.7282849693906</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$150,A5,'Species'!$U$2:$U$150))</x:f>
-        <x:v>114372298.81204227</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.3526366633657885</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2252.354073831527</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>113496807.02694955</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>875491.7850927114</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0077138010136693</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0077138010136692916</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>16.5853120462</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>16.5853120462</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$150,A6,'Species'!$U$2:$U$150))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>11474.232535916075</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>11474.232535916075</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>608.2014161528</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.359274336215644</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2287.043032196224</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>608.2014161528</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2654.148314496684</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$150,A7,'Species'!$U$2:$U$150))</x:f>
-        <x:v>1614256.7635564506</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.359274336215644</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2287.043032196224</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1390982.8109841372</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>223273.95257231337</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.160515249224643</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.16051524922464308</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>20497.530624790397</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.050935154593251</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1124.4370694091847</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>20497.530624790397</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1126.1006497337187</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$150,A8,'Species'!$U$2:$U$150))</x:f>
-        <x:v>23082282.554513264</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.050935154593251</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1124.4370694091847</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>23048183.265864328</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>34099.2886489369</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.001479478371705</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0014794783717048921</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>36062.33265316811</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.463399416972191</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>290.66946881424735</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>36062.33265316811</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>394.04486044696057</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$150,A9,'Species'!$U$2:$U$150))</x:f>
-        <x:v>14210176.837709498</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.463399416972191</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>290.66946881424735</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10482219.076499062</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3727957.761210436</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3556458545660859</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.35564585456608583</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>65669.7765202146</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.452448485717718</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>283.43174181026126</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>65669.7765202146</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>297.68705711571454</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$150,A10,'Species'!$U$2:$U$150))</x:f>
-        <x:v>19549042.51374933</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.452448485717718</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>283.43174181026126</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>18612899.14341502</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>936143.3703343123</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0502954087442904</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.05029540874429047</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>177002.419576615</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.320140763025615</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>208.99734208569325</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>177002.419576615</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>235.73788729054485</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$150,A11,'Species'!$U$2:$U$150))</x:f>
-        <x:v>41726176.4363058</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.320140763025615</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>208.99734208569325</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>36993035.23424921</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4733141.202056587</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1279468195049458</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.12794681950494588</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>216020.4285865126</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5757559096498923</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>376.49213631909385</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>216020.4285865126</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>469.11465653466985</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$150,A12,'Species'!$U$2:$U$150))</x:f>
-        <x:v>101338349.16083403</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5757559096498923</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>376.49213631909385</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>81329992.64710239</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>20008356.513731644</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2460144881673552</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.24601448816735505</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>75211.602686996</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.303469985885728</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>201.12681945479716</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>75211.602686996</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>245.37815183585528</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$150,A13,'Species'!$U$2:$U$150))</x:f>
-        <x:v>18455284.063947726</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.303469985885728</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>201.12681945479716</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>15127070.434533382</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>3328213.629414344</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2200170643627342</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.22001706436273416</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>7344.518899896</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.4033127397496536</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>25.311200248884706</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>7344.518899896</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>35.98566640231227</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$150,A14,'Species'!$U$2:$U$150))</x:f>
-        <x:v>264297.40701713494</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.4033127397496536</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>25.311200248884706</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>185898.58860698607</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>78398.81841014887</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.4217289598464582</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.42172895984645814</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>57445.371465267905</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.818514744866257</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>65.8437784388733</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>57445.371465267905</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>114.9426857736241</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$150,A15,'Species'!$U$2:$U$150))</x:f>
-        <x:v>6602925.281481401</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.818514744866257</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>65.8437784388733</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3782420.3110978743</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2820504.9703835268</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.745687876650825</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.745687876650825</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>500.110666233</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.8649245977054623</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>732.6973110418323</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>500.110666233</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>792.7194667947197</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$150,A16,'Species'!$U$2:$U$150))</x:f>
-        <x:v>396447.46067457576</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.8649245977054623</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>732.6973110418323</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>366429.7403722584</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>30017.72030231735</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0819194431975476</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.08191944319754764</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>25621.845891836</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>524.8074602497728</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>25621.845891836</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$150,A17,'Species'!$U$2:$U$150))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>13446535.869405527</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>13446535.869405527</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>102613.9591948124</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.1759270866467624</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>149.94330757491844</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>102613.9591948124</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>153.61688590940915</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$150,A18,'Species'!$U$2:$U$150))</x:f>
-        <x:v>15763236.862342263</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.1759270866467624</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>149.94330757491844</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>15386276.445027886</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>376960.4173143767</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0244997819102746</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.02449978191027449</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>438.59408739</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.6403766657148733</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>436.89458876792884</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>438.59408739</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>550.3240317398725</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$150,A19,'Species'!$U$2:$U$150))</x:f>
-        <x:v>241368.86646973476</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.6403766657148733</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>436.89458876792884</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>191619.3834462991</x:v>
       </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>49749.48302343566</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.2596265687149435</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.25962656871494344</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d14da6b17b848d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ebeeaa91b694efc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12490,7 +11391,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12589,7 +11490,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>651770218.0518247</x:v>
+        <x:v>393540157.69617546</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12603,7 +11504,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>651770218.0518246</x:v>
+        <x:v>564684929.637638</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12617,7 +11518,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-258230060.35564923</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12631,7 +11532,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-87085288.41418672</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12642,9 +11543,9 @@
         <x:v>EEZ_157</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12656,47 +11557,19 @@
         <x:v>EEZ_157</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_157</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_157</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R129fa49af6c84203"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5b29d3f61bc4c29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12743,7 +11616,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
